--- a/data/desempeno/kpi_desempeno_2026-03-07.xlsx
+++ b/data/desempeno/kpi_desempeno_2026-03-07.xlsx
@@ -415,16 +415,16 @@
         <v>311</v>
       </c>
       <c r="F7" s="65">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G7" s="65">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="H7" s="65">
         <v>0</v>
       </c>
       <c r="I7" s="64">
-        <v>2105.00</v>
+        <v>2106.00</v>
       </c>
     </row>
     <row r="8">
@@ -1128,22 +1128,22 @@
         <v>4763</v>
       </c>
       <c r="F30" s="69">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="G30" s="69">
-        <v>34613</v>
+        <v>34614</v>
       </c>
       <c r="H30" s="69">
         <v>0</v>
       </c>
       <c r="I30" s="69">
-        <v>1280.96</v>
+        <v>1281.00</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31" s="0">
         <is>
-          <t xml:space="preserve">Reporte generado: 09-03-2026 07:04 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 11-03-2026 08:30 a. m. </t>
         </is>
       </c>
     </row>
